--- a/artfynd/A 52297-2025 artfynd.xlsx
+++ b/artfynd/A 52297-2025 artfynd.xlsx
@@ -1233,54 +1233,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129615231</v>
+        <v>129618180</v>
       </c>
       <c r="B7" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495360</v>
+        <v>495065</v>
       </c>
       <c r="R7" t="n">
-        <v>7009347</v>
+        <v>7009210</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1312,7 +1303,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1322,7 +1313,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,45 +1340,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129618180</v>
+        <v>129615231</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495065</v>
+        <v>495360</v>
       </c>
       <c r="R8" t="n">
-        <v>7009210</v>
+        <v>7009347</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1670,54 +1670,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129615431</v>
+        <v>129617691</v>
       </c>
       <c r="B11" t="n">
-        <v>98727</v>
+        <v>91549</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495383</v>
+        <v>495139</v>
       </c>
       <c r="R11" t="n">
-        <v>7009358</v>
+        <v>7009245</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1749,7 +1740,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1759,7 +1750,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,22 +1765,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129617691</v>
+        <v>129617635</v>
       </c>
       <c r="B12" t="n">
-        <v>91549</v>
+        <v>79044</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1797,21 +1788,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1821,10 +1812,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495139</v>
+        <v>495169</v>
       </c>
       <c r="R12" t="n">
-        <v>7009245</v>
+        <v>7009234</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1856,7 +1847,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1866,7 +1857,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,57 +1872,66 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129617635</v>
+        <v>129615431</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495169</v>
+        <v>495383</v>
       </c>
       <c r="R13" t="n">
-        <v>7009234</v>
+        <v>7009358</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 52297-2025 artfynd.xlsx
+++ b/artfynd/A 52297-2025 artfynd.xlsx
@@ -1777,45 +1777,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129617635</v>
+        <v>129615431</v>
       </c>
       <c r="B12" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495169</v>
+        <v>495383</v>
       </c>
       <c r="R12" t="n">
-        <v>7009234</v>
+        <v>7009358</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1847,7 +1856,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1857,7 +1866,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1884,54 +1893,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129615431</v>
+        <v>129617635</v>
       </c>
       <c r="B13" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495383</v>
+        <v>495169</v>
       </c>
       <c r="R13" t="n">
-        <v>7009358</v>
+        <v>7009234</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 52297-2025 artfynd.xlsx
+++ b/artfynd/A 52297-2025 artfynd.xlsx
@@ -1233,45 +1233,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129618180</v>
+        <v>129615231</v>
       </c>
       <c r="B7" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495065</v>
+        <v>495360</v>
       </c>
       <c r="R7" t="n">
-        <v>7009210</v>
+        <v>7009347</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1303,7 +1312,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1313,7 +1322,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,54 +1349,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129615231</v>
+        <v>129618180</v>
       </c>
       <c r="B8" t="n">
-        <v>98727</v>
+        <v>79044</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495360</v>
+        <v>495065</v>
       </c>
       <c r="R8" t="n">
-        <v>7009347</v>
+        <v>7009210</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1670,10 +1670,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129617691</v>
+        <v>129617635</v>
       </c>
       <c r="B11" t="n">
-        <v>91549</v>
+        <v>79044</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,21 +1681,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495139</v>
+        <v>495169</v>
       </c>
       <c r="R11" t="n">
-        <v>7009245</v>
+        <v>7009234</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,66 +1765,57 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129615431</v>
+        <v>129617691</v>
       </c>
       <c r="B12" t="n">
-        <v>98727</v>
+        <v>91549</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495383</v>
+        <v>495139</v>
       </c>
       <c r="R12" t="n">
-        <v>7009358</v>
+        <v>7009245</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1856,7 +1847,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1866,7 +1857,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,57 +1872,66 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129617635</v>
+        <v>129615431</v>
       </c>
       <c r="B13" t="n">
-        <v>79044</v>
+        <v>98727</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495169</v>
+        <v>495383</v>
       </c>
       <c r="R13" t="n">
-        <v>7009234</v>
+        <v>7009358</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 52297-2025 artfynd.xlsx
+++ b/artfynd/A 52297-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129617270</v>
       </c>
       <c r="B2" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129618429</v>
       </c>
       <c r="B3" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>129616563</v>
       </c>
       <c r="B4" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>129616687</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>57730</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>129618248</v>
       </c>
       <c r="B6" t="n">
-        <v>91549</v>
+        <v>91577</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>129615231</v>
       </c>
       <c r="B7" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1352,7 +1352,7 @@
         <v>129618180</v>
       </c>
       <c r="B8" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>129616232</v>
       </c>
       <c r="B9" t="n">
-        <v>79044</v>
+        <v>79070</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>129614670</v>
       </c>
       <c r="B10" t="n">
-        <v>90935</v>
+        <v>90963</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,10 +1670,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129617635</v>
+        <v>129617691</v>
       </c>
       <c r="B11" t="n">
-        <v>79044</v>
+        <v>91577</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,21 +1681,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495169</v>
+        <v>495139</v>
       </c>
       <c r="R11" t="n">
-        <v>7009234</v>
+        <v>7009245</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,22 +1765,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129617691</v>
+        <v>129617635</v>
       </c>
       <c r="B12" t="n">
-        <v>91549</v>
+        <v>79070</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1788,21 +1788,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495139</v>
+        <v>495169</v>
       </c>
       <c r="R12" t="n">
-        <v>7009245</v>
+        <v>7009234</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,12 +1872,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1887,7 +1887,7 @@
         <v>129615431</v>
       </c>
       <c r="B13" t="n">
-        <v>98727</v>
+        <v>98756</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 52297-2025 artfynd.xlsx
+++ b/artfynd/A 52297-2025 artfynd.xlsx
@@ -1233,54 +1233,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129615231</v>
+        <v>129618180</v>
       </c>
       <c r="B7" t="n">
-        <v>98756</v>
+        <v>79070</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495360</v>
+        <v>495065</v>
       </c>
       <c r="R7" t="n">
-        <v>7009347</v>
+        <v>7009210</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1312,7 +1303,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1322,7 +1313,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,45 +1340,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129618180</v>
+        <v>129615231</v>
       </c>
       <c r="B8" t="n">
-        <v>79070</v>
+        <v>98756</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495065</v>
+        <v>495360</v>
       </c>
       <c r="R8" t="n">
-        <v>7009210</v>
+        <v>7009347</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1670,10 +1670,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129617691</v>
+        <v>129617635</v>
       </c>
       <c r="B11" t="n">
-        <v>91577</v>
+        <v>79070</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,21 +1681,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495139</v>
+        <v>495169</v>
       </c>
       <c r="R11" t="n">
-        <v>7009245</v>
+        <v>7009234</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,22 +1765,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129617635</v>
+        <v>129617691</v>
       </c>
       <c r="B12" t="n">
-        <v>79070</v>
+        <v>91577</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1788,21 +1788,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495169</v>
+        <v>495139</v>
       </c>
       <c r="R12" t="n">
-        <v>7009234</v>
+        <v>7009245</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,12 +1872,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 52297-2025 artfynd.xlsx
+++ b/artfynd/A 52297-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129617270</v>
       </c>
       <c r="B2" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129618429</v>
       </c>
       <c r="B3" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>129616563</v>
       </c>
       <c r="B4" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>129616687</v>
       </c>
       <c r="B5" t="n">
-        <v>57730</v>
+        <v>57735</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>129618248</v>
       </c>
       <c r="B6" t="n">
-        <v>91577</v>
+        <v>91583</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>129618180</v>
       </c>
       <c r="B7" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>129615231</v>
       </c>
       <c r="B8" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>129616232</v>
       </c>
       <c r="B9" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>129614670</v>
       </c>
       <c r="B10" t="n">
-        <v>90963</v>
+        <v>90969</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>129617635</v>
       </c>
       <c r="B11" t="n">
-        <v>79070</v>
+        <v>79075</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>129617691</v>
       </c>
       <c r="B12" t="n">
-        <v>91577</v>
+        <v>91583</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>129615431</v>
       </c>
       <c r="B13" t="n">
-        <v>98756</v>
+        <v>98768</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 52297-2025 artfynd.xlsx
+++ b/artfynd/A 52297-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129617270</v>
       </c>
       <c r="B2" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129618429</v>
       </c>
       <c r="B3" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>129616563</v>
       </c>
       <c r="B4" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>129616687</v>
       </c>
       <c r="B5" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>129618248</v>
       </c>
       <c r="B6" t="n">
-        <v>91583</v>
+        <v>91584</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,45 +1233,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129618180</v>
+        <v>129615231</v>
       </c>
       <c r="B7" t="n">
-        <v>79075</v>
+        <v>98769</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495065</v>
+        <v>495360</v>
       </c>
       <c r="R7" t="n">
-        <v>7009210</v>
+        <v>7009347</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1303,7 +1312,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1313,7 +1322,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,54 +1349,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129615231</v>
+        <v>129618180</v>
       </c>
       <c r="B8" t="n">
-        <v>98768</v>
+        <v>79076</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495360</v>
+        <v>495065</v>
       </c>
       <c r="R8" t="n">
-        <v>7009347</v>
+        <v>7009210</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,7 +1459,7 @@
         <v>129616232</v>
       </c>
       <c r="B9" t="n">
-        <v>79075</v>
+        <v>79076</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>129614670</v>
       </c>
       <c r="B10" t="n">
-        <v>90969</v>
+        <v>90970</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,10 +1670,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129617635</v>
+        <v>129617691</v>
       </c>
       <c r="B11" t="n">
-        <v>79075</v>
+        <v>91584</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,21 +1681,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495169</v>
+        <v>495139</v>
       </c>
       <c r="R11" t="n">
-        <v>7009234</v>
+        <v>7009245</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,22 +1765,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129617691</v>
+        <v>129617635</v>
       </c>
       <c r="B12" t="n">
-        <v>91583</v>
+        <v>79076</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1788,21 +1788,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495139</v>
+        <v>495169</v>
       </c>
       <c r="R12" t="n">
-        <v>7009245</v>
+        <v>7009234</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,12 +1872,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1887,7 +1887,7 @@
         <v>129615431</v>
       </c>
       <c r="B13" t="n">
-        <v>98768</v>
+        <v>98769</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 52297-2025 artfynd.xlsx
+++ b/artfynd/A 52297-2025 artfynd.xlsx
@@ -1670,10 +1670,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129617691</v>
+        <v>129617635</v>
       </c>
       <c r="B11" t="n">
-        <v>91584</v>
+        <v>79076</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,21 +1681,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495139</v>
+        <v>495169</v>
       </c>
       <c r="R11" t="n">
-        <v>7009245</v>
+        <v>7009234</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,22 +1765,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129617635</v>
+        <v>129617691</v>
       </c>
       <c r="B12" t="n">
-        <v>79076</v>
+        <v>91584</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1788,21 +1788,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495169</v>
+        <v>495139</v>
       </c>
       <c r="R12" t="n">
-        <v>7009234</v>
+        <v>7009245</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,12 +1872,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 52297-2025 artfynd.xlsx
+++ b/artfynd/A 52297-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129617270</v>
       </c>
       <c r="B2" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129618429</v>
       </c>
       <c r="B3" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>129618248</v>
       </c>
       <c r="B6" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,54 +1233,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129615231</v>
+        <v>129618180</v>
       </c>
       <c r="B7" t="n">
-        <v>98769</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495360</v>
+        <v>495065</v>
       </c>
       <c r="R7" t="n">
-        <v>7009347</v>
+        <v>7009210</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1312,7 +1303,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1322,7 +1313,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,45 +1340,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129618180</v>
+        <v>129615231</v>
       </c>
       <c r="B8" t="n">
-        <v>79076</v>
+        <v>98774</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495065</v>
+        <v>495360</v>
       </c>
       <c r="R8" t="n">
-        <v>7009210</v>
+        <v>7009347</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,7 +1459,7 @@
         <v>129616232</v>
       </c>
       <c r="B9" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>129614670</v>
       </c>
       <c r="B10" t="n">
-        <v>90970</v>
+        <v>90975</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>129617635</v>
       </c>
       <c r="B11" t="n">
-        <v>79076</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1780,7 +1780,7 @@
         <v>129617691</v>
       </c>
       <c r="B12" t="n">
-        <v>91584</v>
+        <v>91589</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1887,7 +1887,7 @@
         <v>129615431</v>
       </c>
       <c r="B13" t="n">
-        <v>98769</v>
+        <v>98774</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>

--- a/artfynd/A 52297-2025 artfynd.xlsx
+++ b/artfynd/A 52297-2025 artfynd.xlsx
@@ -1670,10 +1670,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129617635</v>
+        <v>129617691</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>91589</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,21 +1681,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495169</v>
+        <v>495139</v>
       </c>
       <c r="R11" t="n">
-        <v>7009234</v>
+        <v>7009245</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,22 +1765,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129617691</v>
+        <v>129617635</v>
       </c>
       <c r="B12" t="n">
-        <v>91589</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1788,21 +1788,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495139</v>
+        <v>495169</v>
       </c>
       <c r="R12" t="n">
-        <v>7009245</v>
+        <v>7009234</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,12 +1872,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 52297-2025 artfynd.xlsx
+++ b/artfynd/A 52297-2025 artfynd.xlsx
@@ -1670,10 +1670,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129617691</v>
+        <v>129617635</v>
       </c>
       <c r="B11" t="n">
-        <v>91589</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,21 +1681,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495139</v>
+        <v>495169</v>
       </c>
       <c r="R11" t="n">
-        <v>7009245</v>
+        <v>7009234</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,22 +1765,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129617635</v>
+        <v>129617691</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>91589</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1788,21 +1788,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1812,10 +1812,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495169</v>
+        <v>495139</v>
       </c>
       <c r="R12" t="n">
-        <v>7009234</v>
+        <v>7009245</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1847,7 +1847,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1857,7 +1857,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1872,12 +1872,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>

--- a/artfynd/A 52297-2025 artfynd.xlsx
+++ b/artfynd/A 52297-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129617270</v>
       </c>
       <c r="B2" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129618429</v>
       </c>
       <c r="B3" t="n">
-        <v>98774</v>
+        <v>98778</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>129618248</v>
       </c>
       <c r="B6" t="n">
-        <v>91589</v>
+        <v>91593</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,45 +1233,54 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129618180</v>
+        <v>129615231</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>98778</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495065</v>
+        <v>495360</v>
       </c>
       <c r="R7" t="n">
-        <v>7009210</v>
+        <v>7009347</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1303,7 +1312,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1313,7 +1322,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1340,54 +1349,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129615231</v>
+        <v>129618180</v>
       </c>
       <c r="B8" t="n">
-        <v>98774</v>
+        <v>79081</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495360</v>
+        <v>495065</v>
       </c>
       <c r="R8" t="n">
-        <v>7009347</v>
+        <v>7009210</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1566,7 +1566,7 @@
         <v>129614670</v>
       </c>
       <c r="B10" t="n">
-        <v>90975</v>
+        <v>90979</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,10 +1670,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129617691</v>
+        <v>129617635</v>
       </c>
       <c r="B11" t="n">
-        <v>91589</v>
+        <v>79081</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,21 +1681,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1705,10 +1705,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495139</v>
+        <v>495169</v>
       </c>
       <c r="R11" t="n">
-        <v>7009245</v>
+        <v>7009234</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1740,7 +1740,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1750,7 +1750,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1765,57 +1765,66 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129617635</v>
+        <v>129615431</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>98778</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495169</v>
+        <v>495383</v>
       </c>
       <c r="R12" t="n">
-        <v>7009234</v>
+        <v>7009358</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1847,7 +1856,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1857,7 +1866,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1884,54 +1893,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129615431</v>
+        <v>129617691</v>
       </c>
       <c r="B13" t="n">
-        <v>98774</v>
+        <v>91593</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495383</v>
+        <v>495139</v>
       </c>
       <c r="R13" t="n">
-        <v>7009358</v>
+        <v>7009245</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1988,12 +1988,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 52297-2025 artfynd.xlsx
+++ b/artfynd/A 52297-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129617270</v>
       </c>
       <c r="B2" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129618429</v>
       </c>
       <c r="B3" t="n">
-        <v>98778</v>
+        <v>98780</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>129618248</v>
       </c>
       <c r="B6" t="n">
-        <v>91593</v>
+        <v>91595</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1233,54 +1233,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129615231</v>
+        <v>129618180</v>
       </c>
       <c r="B7" t="n">
-        <v>98778</v>
+        <v>79081</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495360</v>
+        <v>495065</v>
       </c>
       <c r="R7" t="n">
-        <v>7009347</v>
+        <v>7009210</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1312,7 +1303,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1322,7 +1313,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1349,45 +1340,54 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129618180</v>
+        <v>129615231</v>
       </c>
       <c r="B8" t="n">
-        <v>79081</v>
+        <v>98780</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>495065</v>
+        <v>495360</v>
       </c>
       <c r="R8" t="n">
-        <v>7009210</v>
+        <v>7009347</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1429,7 +1429,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1566,7 +1566,7 @@
         <v>129614670</v>
       </c>
       <c r="B10" t="n">
-        <v>90979</v>
+        <v>90981</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,45 +1670,54 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129617635</v>
+        <v>129615431</v>
       </c>
       <c r="B11" t="n">
-        <v>79081</v>
+        <v>98780</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
           <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495169</v>
+        <v>495383</v>
       </c>
       <c r="R11" t="n">
-        <v>7009234</v>
+        <v>7009358</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1740,7 +1749,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1750,7 +1759,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1777,54 +1786,45 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129615431</v>
+        <v>129617691</v>
       </c>
       <c r="B12" t="n">
-        <v>98778</v>
+        <v>91595</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495383</v>
+        <v>495139</v>
       </c>
       <c r="R12" t="n">
-        <v>7009358</v>
+        <v>7009245</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1856,7 +1856,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1866,7 +1866,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,22 +1881,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129617691</v>
+        <v>129617635</v>
       </c>
       <c r="B13" t="n">
-        <v>91593</v>
+        <v>79081</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1904,21 +1904,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1928,10 +1928,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495139</v>
+        <v>495169</v>
       </c>
       <c r="R13" t="n">
-        <v>7009245</v>
+        <v>7009234</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1988,12 +1988,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>

--- a/artfynd/A 52297-2025 artfynd.xlsx
+++ b/artfynd/A 52297-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1998,6 +1998,629 @@
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>129910926</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91897</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>658</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bringåsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>495289</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7009250</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>129910928</v>
+      </c>
+      <c r="B15" t="n">
+        <v>98785</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bringåsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>495151</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7009234</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor.</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>129910927</v>
+      </c>
+      <c r="B16" t="n">
+        <v>98785</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bringåsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>495297</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7009282</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Flera plantor på fyndplatsen.</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>129910924</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57736</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bringåsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>495163</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7009240</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på tall.</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM17" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129910925</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57896</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bringåsmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>495365</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7009285</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Östersund</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Kyrkås</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kristian Zackrisson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 52297-2025 artfynd.xlsx
+++ b/artfynd/A 52297-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129617270</v>
       </c>
       <c r="B2" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129618429</v>
       </c>
       <c r="B3" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>129615231</v>
       </c>
       <c r="B8" t="n">
-        <v>98780</v>
+        <v>98790</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1670,54 +1670,45 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129615431</v>
+        <v>129617691</v>
       </c>
       <c r="B11" t="n">
-        <v>98780</v>
+        <v>91595</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
           <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495383</v>
+        <v>495139</v>
       </c>
       <c r="R11" t="n">
-        <v>7009358</v>
+        <v>7009245</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1749,7 +1740,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1759,7 +1750,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1774,22 +1765,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129617691</v>
+        <v>129617635</v>
       </c>
       <c r="B12" t="n">
-        <v>91595</v>
+        <v>79081</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1797,21 +1788,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1821,10 +1812,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495139</v>
+        <v>495169</v>
       </c>
       <c r="R12" t="n">
-        <v>7009245</v>
+        <v>7009234</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1856,7 +1847,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1866,7 +1857,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:20</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1881,57 +1872,66 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129617635</v>
+        <v>129615431</v>
       </c>
       <c r="B13" t="n">
-        <v>79081</v>
+        <v>98790</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495169</v>
+        <v>495383</v>
       </c>
       <c r="R13" t="n">
-        <v>7009234</v>
+        <v>7009358</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2133,7 +2133,7 @@
         <v>129910928</v>
       </c>
       <c r="B15" t="n">
-        <v>98785</v>
+        <v>98790</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>129910927</v>
       </c>
       <c r="B16" t="n">
-        <v>98785</v>
+        <v>98790</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 52297-2025 artfynd.xlsx
+++ b/artfynd/A 52297-2025 artfynd.xlsx
@@ -2003,7 +2003,7 @@
         <v>129910926</v>
       </c>
       <c r="B14" t="n">
-        <v>91897</v>
+        <v>91900</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>129910928</v>
       </c>
       <c r="B15" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>129910927</v>
       </c>
       <c r="B16" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>129910924</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>129910925</v>
       </c>
       <c r="B18" t="n">
-        <v>57896</v>
+        <v>57895</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 52297-2025 artfynd.xlsx
+++ b/artfynd/A 52297-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129617270</v>
       </c>
       <c r="B2" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>129618429</v>
       </c>
       <c r="B3" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>129616563</v>
       </c>
       <c r="B4" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>129616687</v>
       </c>
       <c r="B5" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1129,7 +1129,7 @@
         <v>129618248</v>
       </c>
       <c r="B6" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1236,7 +1236,7 @@
         <v>129618180</v>
       </c>
       <c r="B7" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1343,7 +1343,7 @@
         <v>129615231</v>
       </c>
       <c r="B8" t="n">
-        <v>98790</v>
+        <v>98794</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>129616232</v>
       </c>
       <c r="B9" t="n">
-        <v>79081</v>
+        <v>79084</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1566,7 +1566,7 @@
         <v>129614670</v>
       </c>
       <c r="B10" t="n">
-        <v>90981</v>
+        <v>90984</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1673,7 +1673,7 @@
         <v>129617691</v>
       </c>
       <c r="B11" t="n">
-        <v>91595</v>
+        <v>91598</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1777,45 +1777,54 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129617635</v>
+        <v>129615431</v>
       </c>
       <c r="B12" t="n">
-        <v>79081</v>
+        <v>98794</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
           <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495169</v>
+        <v>495383</v>
       </c>
       <c r="R12" t="n">
-        <v>7009234</v>
+        <v>7009358</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1847,7 +1856,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1857,7 +1866,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1884,54 +1893,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129615431</v>
+        <v>129617635</v>
       </c>
       <c r="B13" t="n">
-        <v>98790</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495383</v>
+        <v>495169</v>
       </c>
       <c r="R13" t="n">
-        <v>7009358</v>
+        <v>7009234</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1973,7 +1973,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 52297-2025 artfynd.xlsx
+++ b/artfynd/A 52297-2025 artfynd.xlsx
@@ -2003,7 +2003,7 @@
         <v>129910926</v>
       </c>
       <c r="B14" t="n">
-        <v>91937</v>
+        <v>91939</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>129910928</v>
       </c>
       <c r="B15" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>129910927</v>
       </c>
       <c r="B16" t="n">
-        <v>98831</v>
+        <v>98833</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>

--- a/artfynd/A 52297-2025 artfynd.xlsx
+++ b/artfynd/A 52297-2025 artfynd.xlsx
@@ -2003,7 +2003,7 @@
         <v>129910926</v>
       </c>
       <c r="B14" t="n">
-        <v>91939</v>
+        <v>92026</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>129910928</v>
       </c>
       <c r="B15" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>129910927</v>
       </c>
       <c r="B16" t="n">
-        <v>98833</v>
+        <v>98920</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>129910924</v>
       </c>
       <c r="B17" t="n">
-        <v>57741</v>
+        <v>57826</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>129910925</v>
       </c>
       <c r="B18" t="n">
-        <v>57900</v>
+        <v>57985</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 52297-2025 artfynd.xlsx
+++ b/artfynd/A 52297-2025 artfynd.xlsx
@@ -2003,7 +2003,7 @@
         <v>129910926</v>
       </c>
       <c r="B14" t="n">
-        <v>92026</v>
+        <v>91939</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>129910928</v>
       </c>
       <c r="B15" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2257,7 +2257,7 @@
         <v>129910927</v>
       </c>
       <c r="B16" t="n">
-        <v>98920</v>
+        <v>98833</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2373,7 +2373,7 @@
         <v>129910924</v>
       </c>
       <c r="B17" t="n">
-        <v>57826</v>
+        <v>57741</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2508,7 +2508,7 @@
         <v>129910925</v>
       </c>
       <c r="B18" t="n">
-        <v>57985</v>
+        <v>57900</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>

--- a/artfynd/A 52297-2025 artfynd.xlsx
+++ b/artfynd/A 52297-2025 artfynd.xlsx
@@ -675,52 +675,55 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129617270</v>
+        <v>129910926</v>
       </c>
       <c r="B2" t="n">
-        <v>98797</v>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>teleomorf</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Moarsved, Moarsved, Jmt</t>
+          <t>Bringåsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>495172</v>
+        <v>495289</v>
       </c>
       <c r="R2" t="n">
-        <v>7009232</v>
+        <v>7009250</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -744,22 +747,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>13:04</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>13:04</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -768,72 +761,89 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>Liggande död trädstam, utan markontakt</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Horizontal, dead without ground contact # Picea abies</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129618429</v>
+        <v>129617691</v>
       </c>
       <c r="B3" t="n">
-        <v>98797</v>
+        <v>91905</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1108</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Fr.) Krieglst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>495119</v>
+        <v>495139</v>
       </c>
       <c r="R3" t="n">
-        <v>7009211</v>
+        <v>7009245</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -865,7 +875,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +885,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>13:20</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -902,10 +912,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129616563</v>
+        <v>129618248</v>
       </c>
       <c r="B4" t="n">
-        <v>57740</v>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -913,21 +923,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100109</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -937,10 +947,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>495183</v>
+        <v>495077</v>
       </c>
       <c r="R4" t="n">
-        <v>7009221</v>
+        <v>7009241</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -972,7 +982,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:33</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -982,12 +992,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:33</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>Färska ringhack på gran</t>
+          <t>13:42</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,32 +1019,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129616687</v>
+        <v>129614670</v>
       </c>
       <c r="B5" t="n">
-        <v>57740</v>
+        <v>91282</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>5685</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gullgröppa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudomerulius aureus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Jülich</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1049,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>495180</v>
+        <v>495372</v>
       </c>
       <c r="R5" t="n">
-        <v>7009240</v>
+        <v>7009297</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1084,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:41</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1094,12 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:41</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,44 +1114,44 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129618248</v>
+        <v>129616232</v>
       </c>
       <c r="B6" t="n">
-        <v>91601</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1108</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1161,13 +1161,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>495077</v>
+        <v>495296</v>
       </c>
       <c r="R6" t="n">
-        <v>7009241</v>
+        <v>7009226</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1206,7 +1206,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:42</t>
+          <t>12:24</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1221,22 +1221,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129615231</v>
+        <v>129617635</v>
       </c>
       <c r="B7" t="n">
-        <v>98797</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1244,43 +1244,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>495360</v>
+        <v>495169</v>
       </c>
       <c r="R7" t="n">
-        <v>7009347</v>
+        <v>7009234</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1312,7 +1303,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1322,7 +1313,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,11 +1343,11 @@
         <v>129618180</v>
       </c>
       <c r="B8" t="n">
-        <v>79087</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1456,10 +1447,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129616232</v>
+        <v>129616563</v>
       </c>
       <c r="B9" t="n">
-        <v>79087</v>
+        <v>57953</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1467,21 +1458,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1491,13 +1482,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>495296</v>
+        <v>495183</v>
       </c>
       <c r="R9" t="n">
-        <v>7009226</v>
+        <v>7009221</v>
       </c>
       <c r="S9" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1526,7 +1517,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1536,7 +1527,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>12:24</t>
+          <t>12:33</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1551,44 +1547,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129614670</v>
+        <v>129616687</v>
       </c>
       <c r="B10" t="n">
-        <v>90987</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5685</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gullgröppa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudomerulius aureus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fr.) Jülich</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1598,10 +1594,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>495372</v>
+        <v>495180</v>
       </c>
       <c r="R10" t="n">
-        <v>7009297</v>
+        <v>7009240</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1633,7 +1629,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:41</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1643,7 +1639,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:41</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1658,22 +1659,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129617691</v>
+        <v>129910924</v>
       </c>
       <c r="B11" t="n">
-        <v>91601</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1681,37 +1682,45 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1108</v>
+        <v>100109</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Moarsved, Moarsved, Jmt</t>
+          <t>Bringåsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>495139</v>
+        <v>495163</v>
       </c>
       <c r="R11" t="n">
-        <v>7009245</v>
+        <v>7009240</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1735,22 +1744,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>13:20</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>13:20</t>
+          <t>2025-11-02</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Ringhack, äldre, på tall.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1761,26 +1765,51 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Anne Siivola</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129617635</v>
+        <v>129910925</v>
       </c>
       <c r="B12" t="n">
-        <v>79087</v>
+        <v>58114</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1788,37 +1817,53 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Moarsved, Moarsved, Jmt</t>
+          <t>Bringåsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>495169</v>
+        <v>495365</v>
       </c>
       <c r="R12" t="n">
-        <v>7009234</v>
+        <v>7009285</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1842,22 +1887,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>13:17</t>
+          <t>2025-11-02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1868,26 +1903,31 @@
       </c>
       <c r="AG12" t="b">
         <v>0</v>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>Barrskog</t>
+        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Elin Albrechtsson</t>
+          <t>Kristian Zackrisson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129615431</v>
+        <v>129615231</v>
       </c>
       <c r="B13" t="n">
-        <v>98797</v>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1914,7 +1954,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1928,10 +1968,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>495383</v>
+        <v>495360</v>
       </c>
       <c r="R13" t="n">
-        <v>7009358</v>
+        <v>7009347</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1963,7 +2003,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1973,7 +2013,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:05</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2000,55 +2040,57 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129910926</v>
+        <v>129615431</v>
       </c>
       <c r="B14" t="n">
-        <v>92026</v>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>teleomorf</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Bringåsmyren, Jmt</t>
+          <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>495289</v>
+        <v>495383</v>
       </c>
       <c r="R14" t="n">
-        <v>7009250</v>
+        <v>7009358</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2072,12 +2114,22 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>12:05</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2086,54 +2138,28 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>Liggande död trädstam, utan markontakt</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Horizontal, dead without ground contact # Picea abies</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129910928</v>
+        <v>129617270</v>
       </c>
       <c r="B15" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2160,34 +2186,22 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Bringåsmyren, Jmt</t>
+          <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>495151</v>
+        <v>495172</v>
       </c>
       <c r="R15" t="n">
-        <v>7009234</v>
+        <v>7009232</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2211,17 +2225,22 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Minst 10 plantor.</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:04</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2230,34 +2249,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Elin Albrechtsson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129910927</v>
+        <v>129618429</v>
       </c>
       <c r="B16" t="n">
-        <v>98920</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2282,28 +2295,29 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Bringåsmyren, Jmt</t>
+          <t>Moarsved, Moarsved, Jmt</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>495297</v>
+        <v>495119</v>
       </c>
       <c r="R16" t="n">
-        <v>7009282</v>
+        <v>7009211</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2327,17 +2341,22 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2025-11-02</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Flera plantor på fyndplatsen.</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2346,66 +2365,60 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>Barrskog</t>
-        </is>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kristian Zackrisson</t>
+          <t>Anne Siivola</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129910924</v>
+        <v>129910927</v>
       </c>
       <c r="B17" t="n">
-        <v>57826</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2413,10 +2426,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>495163</v>
+        <v>495297</v>
       </c>
       <c r="R17" t="n">
-        <v>7009240</v>
+        <v>7009282</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2453,7 +2466,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Ringhack, äldre, på tall.</t>
+          <t>Flera plantor på fyndplatsen.</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2462,32 +2475,13 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2505,61 +2499,61 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129910925</v>
+        <v>129910928</v>
       </c>
       <c r="B18" t="n">
-        <v>57985</v>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
           <t>Bringåsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>495365</v>
+        <v>495151</v>
       </c>
       <c r="R18" t="n">
-        <v>7009285</v>
+        <v>7009234</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2594,12 +2588,18 @@
           <t>2025-11-02</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Minst 10 plantor.</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 52297-2025 artfynd.xlsx
+++ b/artfynd/A 52297-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -802,6 +807,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910926</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -909,6 +919,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129617691</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1016,6 +1031,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129618248</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1123,6 +1143,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129614670</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1230,6 +1255,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129616232</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1337,6 +1367,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129617635</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1444,6 +1479,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129618180</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1556,6 +1596,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129616563</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1668,6 +1713,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129616687</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1803,6 +1853,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910924</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1921,6 +1976,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910925</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2037,6 +2097,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129615231</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2153,6 +2218,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129615431</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2264,6 +2334,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129617270</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2380,6 +2455,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129618429</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2496,6 +2576,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910927</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2620,8 +2705,32 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129910928</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>